--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][Raw]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][Raw]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -495,40 +507,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="C2" t="n">
         <v>570</v>
       </c>
       <c r="D2" t="n">
-        <v>8.925525602220251</v>
+        <v>8.990151631732608</v>
       </c>
       <c r="E2" t="n">
         <v>14.02998940265233</v>
       </c>
       <c r="F2" t="n">
-        <v>3.880370122876917</v>
+        <v>3.828819976884008</v>
       </c>
       <c r="G2" t="n">
         <v>3.32952463559042</v>
       </c>
       <c r="H2" t="n">
-        <v>8.987227751414984</v>
+        <v>9.05089827054621</v>
       </c>
       <c r="I2" t="n">
         <v>14.10560097576715</v>
       </c>
       <c r="J2" t="n">
-        <v>5.118373224352165</v>
+        <v>5.05470270522094</v>
       </c>
       <c r="K2" t="n">
-        <v>62662</v>
+        <v>60217</v>
       </c>
       <c r="L2" t="n">
-        <v>1.150817323113348e-90</v>
+        <v>3.656155147727473e-88</v>
       </c>
       <c r="M2" t="n">
-        <v>4.603269292453393e-90</v>
+        <v>1.462462059090989e-87</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -541,40 +553,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="C3" t="n">
         <v>570</v>
       </c>
       <c r="D3" t="n">
-        <v>70.10398819163679</v>
+        <v>70.23884682865139</v>
       </c>
       <c r="E3" t="n">
         <v>79.04120766761035</v>
       </c>
       <c r="F3" t="n">
-        <v>11.21656521667945</v>
+        <v>11.34813835793802</v>
       </c>
       <c r="G3" t="n">
         <v>7.228671303811621</v>
       </c>
       <c r="H3" t="n">
-        <v>70.57194405862165</v>
+        <v>70.6402470297961</v>
       </c>
       <c r="I3" t="n">
         <v>78.6357160650788</v>
       </c>
       <c r="J3" t="n">
-        <v>8.063772006457143</v>
+        <v>7.995469035282696</v>
       </c>
       <c r="K3" t="n">
-        <v>100322</v>
+        <v>97730</v>
       </c>
       <c r="L3" t="n">
-        <v>2.489197404819925e-45</v>
+        <v>2.075648644601362e-42</v>
       </c>
       <c r="M3" t="n">
-        <v>9.9567896192797e-45</v>
+        <v>8.30259457840545e-42</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -587,40 +599,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="C4" t="n">
         <v>570</v>
       </c>
       <c r="D4" t="n">
-        <v>11.41679933468676</v>
+        <v>11.48350365985305</v>
       </c>
       <c r="E4" t="n">
         <v>16.74585137970024</v>
       </c>
       <c r="F4" t="n">
-        <v>3.631634309513948</v>
+        <v>3.582220406027393</v>
       </c>
       <c r="G4" t="n">
         <v>3.372256912409433</v>
       </c>
       <c r="H4" t="n">
-        <v>11.3928756880994</v>
+        <v>11.46561644925975</v>
       </c>
       <c r="I4" t="n">
         <v>16.98508770866685</v>
       </c>
       <c r="J4" t="n">
-        <v>5.59221202056745</v>
+        <v>5.5194712594071</v>
       </c>
       <c r="K4" t="n">
-        <v>56211</v>
+        <v>54145</v>
       </c>
       <c r="L4" t="n">
-        <v>4.998530088574303e-100</v>
+        <v>3.655731032892727e-97</v>
       </c>
       <c r="M4" t="n">
-        <v>1.999412035429721e-99</v>
+        <v>1.462292413157091e-96</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -633,40 +645,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="C5" t="n">
         <v>570</v>
       </c>
       <c r="D5" t="n">
-        <v>94.80169841141614</v>
+        <v>94.62036513236889</v>
       </c>
       <c r="E5" t="n">
         <v>79.82764748247047</v>
       </c>
       <c r="F5" t="n">
-        <v>26.36388367175575</v>
+        <v>26.76392642287756</v>
       </c>
       <c r="G5" t="n">
         <v>30.06975677244978</v>
       </c>
       <c r="H5" t="n">
-        <v>97.56130062496165</v>
+        <v>97.21914174989274</v>
       </c>
       <c r="I5" t="n">
         <v>82.09190306966485</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.46939755529679</v>
+        <v>-15.12723868022789</v>
       </c>
       <c r="K5" t="n">
-        <v>242560</v>
+        <v>230823</v>
       </c>
       <c r="L5" t="n">
-        <v>1.843188756373086e-18</v>
+        <v>1.203926076864382e-17</v>
       </c>
       <c r="M5" t="n">
-        <v>7.372755025492342e-18</v>
+        <v>4.815704307457529e-17</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
